--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>buffIds</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>animconfigs</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>##备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +519,11 @@
           <t>list#sep=|#,int#ref=cfg.buff.TbBuff</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>list#sep=|#,string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,6 +569,11 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>持有buff</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>动画配置名(对应prefab1|prefab2)</t>
         </is>
       </c>
     </row>
@@ -577,17 +597,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>prefabs/player/homo_talk</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Assets\Prefabs\player\Hippo</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Assets\Prefabs\player\homo_talk</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>homo_talk|homo_move</t>
         </is>
       </c>
     </row>
@@ -611,17 +636,124 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Assets\Prefabs\player\Hippo</t>
+          <t>prefabs/npc/coach</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Assets\Prefabs\player\homo_talk</t>
+          <t>Assets\Prefabs\npc\coach</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>coach</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>拳王</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>prefabs/npc/quanwang_bk</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Assets\Prefabs\npc\quanwang_bk</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>quanwang_bk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>乌合之众1</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>prefabs/npc/npc_01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Assets\Prefabs\npc\npc_01</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>npc_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>乌合之众2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>prefabs/npc/npc_02</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Assets\Prefabs\npc\npc_02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>npc_02</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>avatar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>##备注</t>
         </is>
       </c>
@@ -522,6 +527,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>list#sep=|#,string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -615,6 +625,11 @@
           <t>homo_talk|homo_move</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>avatar_hippo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -654,6 +669,11 @@
           <t>coach</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>avatar_coach</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -688,6 +708,11 @@
           <t>quanwang_bk</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>avatar_quanwang</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -722,6 +747,11 @@
           <t>npc_01</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>avatar_mob1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -754,6 +784,11 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>npc_02</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>avatar_mob2</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7488DC-9292-4506-A13B-B3AA658E708F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1B790E-735B-4936-840E-6F617F766488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,6 +273,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -372,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -389,6 +390,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
@@ -1104,10 +1107,10 @@
       <c r="P6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="Q6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="R6" s="7"/>
+      <c r="R6" s="9"/>
       <c r="S6" s="1" t="s">
         <v>39</v>
       </c>
@@ -7401,8 +7404,7 @@
       <c r="AD201" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="S3:T3"/>
+  <mergeCells count="1">
     <mergeCell ref="Q6:R6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>Assets\Prefabs\player\Hippo</t>
+          <t>prefabs/player/Hippo</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>Assets\Prefabs\npc\coach</t>
+          <t>prefabs/npc/coach_fight</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>Assets\Prefabs\npc\quanwang_bk</t>
+          <t>prefabs/npc/quanwang_bk</t>
         </is>
       </c>
       <c r="R6" s="11" t="n"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>Assets\Prefabs\npc\npc_01</t>
+          <t>prefabs/npc/npc_01</t>
         </is>
       </c>
       <c r="R7" s="1" t="n"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Assets\Prefabs\npc\npc_02</t>
+          <t>prefabs/npc/npc_02</t>
         </is>
       </c>
       <c r="R8" s="1" t="n"/>

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -661,7 +661,11 @@
           <t>speed</t>
         </is>
       </c>
-      <c r="V1" s="5" t="n"/>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
       <c r="W1" s="5" t="n"/>
       <c r="X1" s="5" t="n"/>
       <c r="Y1" s="5" t="n"/>
@@ -777,7 +781,11 @@
           <t>int</t>
         </is>
       </c>
-      <c r="V2" s="5" t="n"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>list#sep=|#,int#ref=cfg.skill.TbSkill</t>
+        </is>
+      </c>
       <c r="W2" s="5" t="n"/>
       <c r="X2" s="5" t="n"/>
       <c r="Y2" s="5" t="n"/>
@@ -887,7 +895,11 @@
       <c r="U3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="5" t="n"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>默认技能ID列表(按|分隔)</t>
+        </is>
+      </c>
       <c r="W3" s="5" t="n"/>
       <c r="X3" s="5" t="n"/>
       <c r="Y3" s="5" t="n"/>
@@ -969,7 +981,11 @@
       <c r="U4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="5" t="n"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>1|2|3|4|5|6</t>
+        </is>
+      </c>
       <c r="W4" s="5" t="n"/>
       <c r="X4" s="5" t="n"/>
       <c r="Y4" s="5" t="n"/>
@@ -1051,7 +1067,11 @@
       <c r="U5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="5" t="n"/>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>4|5|6</t>
+        </is>
+      </c>
       <c r="W5" s="5" t="n"/>
       <c r="X5" s="5" t="n"/>
       <c r="Y5" s="5" t="n"/>
@@ -1113,7 +1133,11 @@
       <c r="U6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="V6" s="5" t="n"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>4|5|6</t>
+        </is>
+      </c>
       <c r="W6" s="5" t="n"/>
       <c r="X6" s="5" t="n"/>
       <c r="Y6" s="5" t="n"/>
@@ -1175,7 +1199,7 @@
       <c r="U7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="V7" s="5" t="n"/>
+      <c r="V7" s="5" t="inlineStr"/>
       <c r="W7" s="5" t="n"/>
       <c r="X7" s="5" t="n"/>
       <c r="Y7" s="5" t="n"/>
@@ -1237,7 +1261,7 @@
       <c r="U8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="V8" s="5" t="n"/>
+      <c r="V8" s="5" t="inlineStr"/>
       <c r="W8" s="5" t="n"/>
       <c r="X8" s="5" t="n"/>
       <c r="Y8" s="5" t="n"/>

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="person" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="person" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -926,13 +926,13 @@
         <v>20</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>0</v>
@@ -1012,13 +1012,13 @@
         <v>10</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
         <v>1</v>

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="person" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="person" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>prefabs/npc/coach</t>
+          <t>prefabs/npc/talk/coach</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5653499C-9B85-4B50-AD38-091143F37986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69B0347-FED5-4EBE-A771-B0AA19976CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,10 +223,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/npc/talk/light_talk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>prefabs/npc/light_scene</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -236,6 +232,10 @@
   </si>
   <si>
     <t>avatar_light</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prefabs/npc/talk/light_talk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1150,17 +1150,17 @@
         <v>1</v>
       </c>
       <c r="P7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T7" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="U7" s="1">
         <v>5</v>

--- a/DataTables/Datas/person.xlsx
+++ b/DataTables/Datas/person.xlsx
@@ -1205,8 +1205,14 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
+      <c r="B8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>alien_01</t>
+        </is>
+      </c>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
@@ -1218,11 +1224,17 @@
       <c r="L8" s="5" t="n"/>
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
+      <c r="O8" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>alien_01</t>
+        </is>
+      </c>
       <c r="T8" s="5" t="n"/>
       <c r="U8" s="5" t="n"/>
       <c r="V8" s="5" t="n"/>
@@ -1237,8 +1249,14 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
+      <c r="B9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>alien_02</t>
+        </is>
+      </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
@@ -1250,11 +1268,17 @@
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
+      <c r="O9" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="n"/>
       <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>alien_02</t>
+        </is>
+      </c>
       <c r="T9" s="5" t="n"/>
       <c r="V9" s="5" t="n"/>
       <c r="W9" s="5" t="n"/>
@@ -1268,8 +1292,14 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
+      <c r="B10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>coach_fight</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
@@ -1281,11 +1311,17 @@
       <c r="L10" s="5" t="n"/>
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
+      <c r="O10" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>coach_fight</t>
+        </is>
+      </c>
       <c r="T10" s="5" t="n"/>
       <c r="U10" s="5" t="n"/>
       <c r="V10" s="5" t="n"/>
@@ -1300,8 +1336,14 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
+      <c r="B11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>fog</t>
+        </is>
+      </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
@@ -1313,11 +1355,17 @@
       <c r="L11" s="5" t="n"/>
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
+      <c r="O11" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>fog</t>
+        </is>
+      </c>
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="5" t="n"/>
       <c r="V11" s="5" t="n"/>
@@ -1332,8 +1380,14 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
+      <c r="B12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
@@ -1345,11 +1399,17 @@
       <c r="L12" s="5" t="n"/>
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
+      <c r="O12" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="5" t="n"/>
       <c r="V12" s="5" t="n"/>
@@ -1364,8 +1424,14 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
+      <c r="B13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>npc_01</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
@@ -1377,11 +1443,17 @@
       <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
+      <c r="O13" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>npc_01</t>
+        </is>
+      </c>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="5" t="n"/>
       <c r="V13" s="5" t="n"/>
@@ -1396,8 +1468,14 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
+      <c r="B14" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>npc_02</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
@@ -1409,11 +1487,17 @@
       <c r="L14" s="5" t="n"/>
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
+      <c r="O14" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>npc_02</t>
+        </is>
+      </c>
       <c r="T14" s="5" t="n"/>
       <c r="U14" s="5" t="n"/>
       <c r="V14" s="5" t="n"/>
@@ -1428,8 +1512,14 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
+      <c r="B15" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>quanwang_pixel</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
@@ -1441,11 +1531,17 @@
       <c r="L15" s="5" t="n"/>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
+      <c r="O15" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>quanwang_pixel</t>
+        </is>
+      </c>
       <c r="T15" s="5" t="n"/>
       <c r="U15" s="5" t="n"/>
       <c r="V15" s="5" t="n"/>
